--- a/artfynd/A 21811-2023 artfynd.xlsx
+++ b/artfynd/A 21811-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136704853</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21811-2023 artfynd.xlsx
+++ b/artfynd/A 21811-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136704853</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21811-2023 artfynd.xlsx
+++ b/artfynd/A 21811-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136704853</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21811-2023 artfynd.xlsx
+++ b/artfynd/A 21811-2023 artfynd.xlsx
@@ -713,11 +713,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stockholmsledet, Bl</t>

--- a/artfynd/A 21811-2023 artfynd.xlsx
+++ b/artfynd/A 21811-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136704853</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
